--- a/uploaded_files/FinancialData.xlsx
+++ b/uploaded_files/FinancialData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\REPORT\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\wealth_tracker_backend\uploaded_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29831541-F10D-4455-865E-E75923125273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C05F39C-E8A9-4ACF-A5BD-A662ACFA6953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{7780D1AE-CE50-4F92-8C33-5CFDD4A6A385}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="39">
   <si>
     <t>FINANCIAL_YEAR</t>
   </si>
@@ -145,6 +145,15 @@
   </si>
   <si>
     <t>INTEREST</t>
+  </si>
+  <si>
+    <t>FD</t>
+  </si>
+  <si>
+    <t>FD_25_26_int_7</t>
+  </si>
+  <si>
+    <t>sell</t>
   </si>
 </sst>
 </file>
@@ -514,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B799C6CD-3D83-4400-974A-6738F2A05447}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -1466,6 +1475,206 @@
         <v>1250</v>
       </c>
     </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>2526</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45748</v>
+      </c>
+      <c r="C48">
+        <v>127407</v>
+      </c>
+      <c r="D48">
+        <v>10660</v>
+      </c>
+      <c r="E48">
+        <v>2350</v>
+      </c>
+      <c r="F48">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>2526</v>
+      </c>
+      <c r="B49" s="1">
+        <v>45778</v>
+      </c>
+      <c r="C49">
+        <v>127407</v>
+      </c>
+      <c r="D49">
+        <v>10951</v>
+      </c>
+      <c r="E49">
+        <v>2350</v>
+      </c>
+      <c r="F49">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>2526</v>
+      </c>
+      <c r="B50" s="1">
+        <v>45809</v>
+      </c>
+      <c r="C50">
+        <v>127408</v>
+      </c>
+      <c r="D50">
+        <v>10659</v>
+      </c>
+      <c r="E50">
+        <v>2350</v>
+      </c>
+      <c r="F50">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>2526</v>
+      </c>
+      <c r="B51" s="1">
+        <v>45839</v>
+      </c>
+      <c r="C51">
+        <v>127408</v>
+      </c>
+      <c r="D51">
+        <v>10659</v>
+      </c>
+      <c r="E51">
+        <v>2350</v>
+      </c>
+      <c r="F51">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>2526</v>
+      </c>
+      <c r="B52" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C52">
+        <v>127408</v>
+      </c>
+      <c r="D52">
+        <v>10659</v>
+      </c>
+      <c r="E52">
+        <v>2350</v>
+      </c>
+      <c r="F52">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>2526</v>
+      </c>
+      <c r="B53" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C53">
+        <v>149848</v>
+      </c>
+      <c r="D53">
+        <v>16552</v>
+      </c>
+      <c r="E53">
+        <v>2350</v>
+      </c>
+      <c r="F53">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>2526</v>
+      </c>
+      <c r="B54" s="1">
+        <v>45931</v>
+      </c>
+      <c r="C54">
+        <v>149848</v>
+      </c>
+      <c r="D54">
+        <v>16552</v>
+      </c>
+      <c r="E54">
+        <v>2350</v>
+      </c>
+      <c r="F54">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>2526</v>
+      </c>
+      <c r="B55" s="1">
+        <v>45962</v>
+      </c>
+      <c r="C55">
+        <v>149848</v>
+      </c>
+      <c r="D55">
+        <v>16552</v>
+      </c>
+      <c r="E55">
+        <v>2350</v>
+      </c>
+      <c r="F55">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>2526</v>
+      </c>
+      <c r="B56" s="1">
+        <v>45992</v>
+      </c>
+      <c r="C56">
+        <v>149848</v>
+      </c>
+      <c r="D56">
+        <v>16552</v>
+      </c>
+      <c r="E56">
+        <v>2350</v>
+      </c>
+      <c r="F56">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>2526</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C57">
+        <v>146496</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>2350</v>
+      </c>
+      <c r="F57">
+        <v>1250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1473,7 +1682,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2389D1D-F723-4623-A734-6459728F657D}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
@@ -1483,7 +1692,7 @@
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -1952,6 +2161,240 @@
       </c>
       <c r="H18">
         <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>312000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>5534</v>
       </c>
     </row>
   </sheetData>
@@ -1963,7 +2406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4760DB9E-5821-49E8-B842-9EABEB8E142E}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
@@ -2611,6 +3054,106 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>2526</v>
+      </c>
+      <c r="B33" s="1">
+        <v>45786</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33">
+        <v>2619</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>2526</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45838</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34">
+        <v>238</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>2526</v>
+      </c>
+      <c r="B35" s="1">
+        <v>45930</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35">
+        <v>126</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>2526</v>
+      </c>
+      <c r="B36" s="1">
+        <v>45900</v>
+      </c>
+      <c r="C36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36">
+        <v>7497</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>2526</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46022</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>222</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2618,7 +3161,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0E7D11-5DD3-425F-AF3D-D34510F17951}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -2720,6 +3263,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2526</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>60000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/uploaded_files/FinancialData.xlsx
+++ b/uploaded_files/FinancialData.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\wealth_tracker_backend\uploaded_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C05F39C-E8A9-4ACF-A5BD-A662ACFA6953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698C3851-60C9-4AB3-A6F2-C0A1407E0ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{7780D1AE-CE50-4F92-8C33-5CFDD4A6A385}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{7780D1AE-CE50-4F92-8C33-5CFDD4A6A385}"/>
   </bookViews>
   <sheets>
     <sheet name="Income" sheetId="1" r:id="rId1"/>
     <sheet name="Invest" sheetId="2" r:id="rId2"/>
     <sheet name="Interest" sheetId="3" r:id="rId3"/>
-    <sheet name="Loan" sheetId="4" r:id="rId4"/>
+    <sheet name="Tax" sheetId="5" r:id="rId4"/>
+    <sheet name="Loan" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="47">
   <si>
     <t>FINANCIAL_YEAR</t>
   </si>
@@ -48,9 +49,6 @@
     <t>SALARY</t>
   </si>
   <si>
-    <t>TAX</t>
-  </si>
-  <si>
     <t>EPF</t>
   </si>
   <si>
@@ -154,6 +152,33 @@
   </si>
   <si>
     <t>sell</t>
+  </si>
+  <si>
+    <t>``</t>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+  </si>
+  <si>
+    <t>TDS</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>Juspay</t>
+  </si>
+  <si>
+    <t>Belong</t>
+  </si>
+  <si>
+    <t>REFUND</t>
+  </si>
+  <si>
+    <t>TDS_BONDS</t>
+  </si>
+  <si>
+    <t>CREDIT_IN</t>
   </si>
 </sst>
 </file>
@@ -523,1155 +548,1326 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B799C6CD-3D83-4400-974A-6738F2A05447}">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.08984375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2122</v>
       </c>
       <c r="B2" s="1">
         <v>44348</v>
       </c>
-      <c r="C2">
-        <v>56970</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E2">
+        <v>61034</v>
+      </c>
+      <c r="F2">
         <v>2653</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1411</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2122</v>
       </c>
       <c r="B3" s="1">
         <v>44378</v>
       </c>
-      <c r="C3">
-        <v>56316</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E3">
+        <v>59916</v>
+      </c>
+      <c r="F3">
         <v>2350</v>
       </c>
-      <c r="F3">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2122</v>
       </c>
       <c r="B4" s="1">
         <v>44409</v>
       </c>
-      <c r="C4">
-        <v>28316</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E4">
+        <v>31916</v>
+      </c>
+      <c r="F4">
         <v>2350</v>
       </c>
-      <c r="F4">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2122</v>
       </c>
       <c r="B5" s="1">
         <v>44440</v>
       </c>
-      <c r="C5">
-        <v>28316</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E5">
+        <v>31916</v>
+      </c>
+      <c r="F5">
         <v>2350</v>
       </c>
-      <c r="F5">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2122</v>
       </c>
       <c r="B6" s="1">
         <v>44470</v>
       </c>
-      <c r="C6">
-        <v>28316</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E6">
+        <v>31916</v>
+      </c>
+      <c r="F6">
         <v>2350</v>
       </c>
-      <c r="F6">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2122</v>
       </c>
       <c r="B7" s="1">
         <v>44501</v>
       </c>
-      <c r="C7">
-        <v>36878</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E7">
+        <v>40478</v>
+      </c>
+      <c r="F7">
         <v>2350</v>
       </c>
-      <c r="F7">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2122</v>
       </c>
       <c r="B8" s="1">
         <v>44531</v>
       </c>
-      <c r="C8">
-        <v>28316</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E8">
+        <v>31916</v>
+      </c>
+      <c r="F8">
         <v>2350</v>
       </c>
-      <c r="F8">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2122</v>
       </c>
       <c r="B9" s="1">
         <v>44562</v>
       </c>
-      <c r="C9">
-        <v>28316</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E9">
+        <v>31916</v>
+      </c>
+      <c r="F9">
         <v>2350</v>
       </c>
-      <c r="F9">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2122</v>
       </c>
       <c r="B10" s="1">
         <v>44593</v>
       </c>
-      <c r="C10">
-        <v>28316</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E10">
+        <v>31916</v>
+      </c>
+      <c r="F10">
         <v>2350</v>
       </c>
-      <c r="F10">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2122</v>
       </c>
       <c r="B11" s="1">
         <v>44622</v>
       </c>
-      <c r="C11">
-        <v>28326</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E11">
+        <v>31926</v>
+      </c>
+      <c r="F11">
         <v>2350</v>
       </c>
-      <c r="F11">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2223</v>
       </c>
       <c r="B12" s="1">
         <v>44652</v>
       </c>
-      <c r="C12">
-        <v>28316</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E12">
+        <v>31916</v>
+      </c>
+      <c r="F12">
         <v>2350</v>
       </c>
-      <c r="F12">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2223</v>
       </c>
       <c r="B13" s="1">
         <v>44682</v>
       </c>
-      <c r="C13">
-        <v>44460</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E13">
+        <v>48060</v>
+      </c>
+      <c r="F13">
         <v>2350</v>
       </c>
-      <c r="F13">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2223</v>
       </c>
       <c r="B14" s="1">
         <v>44713</v>
       </c>
-      <c r="C14">
-        <v>171715</v>
-      </c>
-      <c r="D14">
-        <v>200</v>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E14">
+        <v>176115</v>
+      </c>
+      <c r="F14">
         <v>2742</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>1458</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2223</v>
       </c>
       <c r="B15" s="1">
         <v>44743</v>
       </c>
-      <c r="C15">
-        <v>63000</v>
-      </c>
-      <c r="D15">
-        <v>200</v>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E15">
+        <v>73200</v>
+      </c>
+      <c r="F15">
         <v>8750</v>
       </c>
-      <c r="F15">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2223</v>
       </c>
       <c r="B16" s="1">
         <v>44774</v>
       </c>
-      <c r="C16">
-        <v>63000</v>
-      </c>
-      <c r="D16">
-        <v>200</v>
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E16">
+        <v>73200</v>
+      </c>
+      <c r="F16">
         <v>8750</v>
       </c>
-      <c r="F16">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2223</v>
       </c>
       <c r="B17" s="1">
         <v>44805</v>
       </c>
-      <c r="C17">
-        <v>63000</v>
-      </c>
-      <c r="D17">
-        <v>200</v>
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E17">
+        <v>73200</v>
+      </c>
+      <c r="F17">
         <v>8750</v>
       </c>
-      <c r="F17">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2223</v>
       </c>
       <c r="B18" s="1">
         <v>44835</v>
       </c>
-      <c r="C18">
-        <v>63000</v>
-      </c>
-      <c r="D18">
-        <v>200</v>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E18">
+        <v>73200</v>
+      </c>
+      <c r="F18">
         <v>8750</v>
       </c>
-      <c r="F18">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2223</v>
       </c>
       <c r="B19" s="1">
         <v>44866</v>
       </c>
-      <c r="C19">
-        <v>63000</v>
-      </c>
-      <c r="D19">
-        <v>200</v>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E19">
+        <v>73200</v>
+      </c>
+      <c r="F19">
         <v>8750</v>
       </c>
-      <c r="F19">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2223</v>
       </c>
       <c r="B20" s="1">
         <v>44896</v>
       </c>
-      <c r="C20">
-        <v>63000</v>
-      </c>
-      <c r="D20">
-        <v>200</v>
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E20">
+        <v>73200</v>
+      </c>
+      <c r="F20">
         <v>8750</v>
       </c>
-      <c r="F20">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2223</v>
       </c>
       <c r="B21" s="1">
         <v>44927</v>
       </c>
-      <c r="C21">
-        <v>63000</v>
-      </c>
-      <c r="D21">
-        <v>200</v>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E21">
+        <v>73200</v>
+      </c>
+      <c r="F21">
         <v>8750</v>
       </c>
-      <c r="F21">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2223</v>
       </c>
       <c r="B22" s="1">
         <v>44958</v>
       </c>
-      <c r="C22">
-        <v>63000</v>
-      </c>
-      <c r="D22">
-        <v>200</v>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E22">
+        <v>73200</v>
+      </c>
+      <c r="F22">
         <v>8750</v>
       </c>
-      <c r="F22">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2223</v>
       </c>
       <c r="B23" s="1">
         <v>44986</v>
       </c>
-      <c r="C23">
-        <v>63000</v>
-      </c>
-      <c r="D23">
-        <v>200</v>
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E23">
+        <v>73200</v>
+      </c>
+      <c r="F23">
         <v>8750</v>
       </c>
-      <c r="F23">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2324</v>
       </c>
       <c r="B24" s="1">
         <v>45017</v>
       </c>
-      <c r="C24">
-        <v>60225</v>
-      </c>
-      <c r="D24">
-        <v>2975</v>
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E24">
+        <v>73200</v>
+      </c>
+      <c r="F24">
         <v>8750</v>
       </c>
-      <c r="F24">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2324</v>
       </c>
       <c r="B25" s="1">
         <v>45047</v>
       </c>
-      <c r="C25">
-        <v>60347</v>
-      </c>
-      <c r="D25">
-        <v>2853</v>
+      <c r="C25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E25">
+        <v>73200</v>
+      </c>
+      <c r="F25">
         <v>8750</v>
       </c>
-      <c r="F25">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2324</v>
       </c>
       <c r="B26" s="1">
         <v>45078</v>
       </c>
-      <c r="C26">
-        <v>60480</v>
-      </c>
-      <c r="D26">
-        <v>2720</v>
+      <c r="C26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E26">
+        <v>73200</v>
+      </c>
+      <c r="F26">
         <v>8750</v>
       </c>
-      <c r="F26">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2324</v>
       </c>
       <c r="B27" s="1">
         <v>45108</v>
       </c>
-      <c r="C27">
-        <v>60628</v>
-      </c>
-      <c r="D27">
-        <v>2572</v>
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E27">
+        <v>73200</v>
+      </c>
+      <c r="F27">
         <v>8750</v>
       </c>
-      <c r="F27">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2324</v>
       </c>
       <c r="B28" s="1">
         <v>45139</v>
       </c>
-      <c r="C28">
-        <v>60794</v>
-      </c>
-      <c r="D28">
-        <v>2406</v>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E28">
+        <v>73200</v>
+      </c>
+      <c r="F28">
         <v>8750</v>
       </c>
-      <c r="F28">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2324</v>
       </c>
       <c r="B29" s="1">
         <v>45170</v>
       </c>
-      <c r="C29">
-        <v>60981</v>
-      </c>
-      <c r="D29">
-        <v>2215</v>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E29">
+        <v>73196</v>
+      </c>
+      <c r="F29">
         <v>8750</v>
       </c>
-      <c r="F29">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2324</v>
       </c>
       <c r="B30" s="1">
         <v>45200</v>
       </c>
-      <c r="C30">
-        <v>98904</v>
-      </c>
-      <c r="D30">
-        <v>4957</v>
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E30">
+        <v>113861</v>
+      </c>
+      <c r="F30">
         <v>8750</v>
       </c>
-      <c r="F30">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2324</v>
       </c>
       <c r="B31" s="1">
         <v>45231</v>
       </c>
-      <c r="C31">
-        <v>66638</v>
-      </c>
-      <c r="D31">
-        <v>4691</v>
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E31">
+        <v>81329</v>
+      </c>
+      <c r="F31">
         <v>8750</v>
       </c>
-      <c r="F31">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2324</v>
       </c>
       <c r="B32" s="1">
         <v>45261</v>
       </c>
-      <c r="C32">
-        <v>66951</v>
-      </c>
-      <c r="D32">
-        <v>4358</v>
+      <c r="C32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E32">
+        <v>81309</v>
+      </c>
+      <c r="F32">
         <v>8750</v>
       </c>
-      <c r="F32">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2324</v>
       </c>
       <c r="B33" s="1">
         <v>45292</v>
       </c>
-      <c r="C33">
-        <v>67415</v>
-      </c>
-      <c r="D33">
-        <v>3914</v>
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E33">
+        <v>81329</v>
+      </c>
+      <c r="F33">
         <v>8750</v>
       </c>
-      <c r="F33">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2324</v>
       </c>
       <c r="B34" s="1">
         <v>45323</v>
       </c>
-      <c r="C34">
-        <v>76327</v>
-      </c>
-      <c r="D34">
-        <v>4762</v>
+      <c r="C34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E34">
+        <v>91089</v>
+      </c>
+      <c r="F34">
         <v>8750</v>
       </c>
-      <c r="F34">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2324</v>
       </c>
       <c r="B35" s="1">
         <v>45352</v>
       </c>
-      <c r="C35">
-        <v>72604</v>
-      </c>
-      <c r="D35">
-        <v>3605</v>
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E35">
+        <v>86209</v>
+      </c>
+      <c r="F35">
         <v>8750</v>
       </c>
-      <c r="F35">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2425</v>
       </c>
       <c r="B36" s="1">
         <v>45383</v>
       </c>
-      <c r="C36">
-        <v>69153</v>
-      </c>
-      <c r="D36">
-        <v>7056</v>
+      <c r="C36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E36">
+        <v>86209</v>
+      </c>
+      <c r="F36">
         <v>8750</v>
       </c>
-      <c r="F36">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2425</v>
       </c>
       <c r="B37" s="1">
         <v>45413</v>
       </c>
-      <c r="C37">
-        <v>69274</v>
-      </c>
-      <c r="D37">
-        <v>6935</v>
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E37">
+        <v>86209</v>
+      </c>
+      <c r="F37">
         <v>8750</v>
       </c>
-      <c r="F37">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2425</v>
       </c>
       <c r="B38" s="1">
         <v>45444</v>
       </c>
-      <c r="C38">
-        <v>69408</v>
-      </c>
-      <c r="D38">
-        <v>6801</v>
+      <c r="C38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E38">
+        <v>86209</v>
+      </c>
+      <c r="F38">
         <v>8750</v>
       </c>
-      <c r="F38">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G38">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2425</v>
       </c>
       <c r="B39" s="1">
         <v>45474</v>
       </c>
-      <c r="C39">
-        <v>69555</v>
-      </c>
-      <c r="D39">
-        <v>6654</v>
+      <c r="C39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E39">
+        <v>86209</v>
+      </c>
+      <c r="F39">
         <v>8750</v>
       </c>
-      <c r="F39">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G39">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2425</v>
       </c>
       <c r="B40" s="1">
         <v>45535</v>
       </c>
-      <c r="C40">
-        <v>73286</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E40">
+        <v>83286</v>
+      </c>
+      <c r="F40">
         <v>8750</v>
       </c>
-      <c r="F40">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G40">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2425</v>
       </c>
       <c r="B41" s="1">
         <v>45536</v>
       </c>
-      <c r="C41">
-        <v>130625</v>
-      </c>
-      <c r="D41">
-        <v>6320</v>
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>136945</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2425</v>
       </c>
       <c r="B42" s="1">
         <v>45566</v>
       </c>
-      <c r="C42">
-        <v>135346</v>
-      </c>
-      <c r="D42">
-        <v>6321</v>
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>141667</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2425</v>
       </c>
       <c r="B43" s="1">
         <v>45597</v>
       </c>
-      <c r="C43">
-        <v>133546</v>
-      </c>
-      <c r="D43">
-        <v>6321</v>
+      <c r="C43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E43">
+        <v>143467</v>
+      </c>
+      <c r="F43">
         <v>2350</v>
       </c>
-      <c r="F43">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G43">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2425</v>
       </c>
       <c r="B44" s="1">
         <v>45627</v>
       </c>
-      <c r="C44">
-        <v>133546</v>
-      </c>
-      <c r="D44">
-        <v>6321</v>
+      <c r="C44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E44">
+        <v>143467</v>
+      </c>
+      <c r="F44">
         <v>2350</v>
       </c>
-      <c r="F44">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G44">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2425</v>
       </c>
       <c r="B45" s="1">
         <v>45658</v>
       </c>
-      <c r="C45">
-        <v>119875</v>
-      </c>
-      <c r="D45">
-        <v>19992</v>
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E45">
+        <v>143467</v>
+      </c>
+      <c r="F45">
         <v>2350</v>
       </c>
-      <c r="F45">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G45">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2425</v>
       </c>
       <c r="B46" s="1">
         <v>45689</v>
       </c>
-      <c r="C46">
-        <v>119875</v>
-      </c>
-      <c r="D46">
-        <v>19992</v>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E46">
+        <v>143467</v>
+      </c>
+      <c r="F46">
         <v>2350</v>
       </c>
-      <c r="F46">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G46">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2425</v>
       </c>
       <c r="B47" s="1">
         <v>45717</v>
       </c>
-      <c r="C47">
-        <v>119876</v>
-      </c>
-      <c r="D47">
-        <v>19991</v>
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E47">
+        <v>143467</v>
+      </c>
+      <c r="F47">
         <v>2350</v>
       </c>
-      <c r="F47">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G47">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2526</v>
       </c>
       <c r="B48" s="1">
         <v>45748</v>
       </c>
-      <c r="C48">
-        <v>127407</v>
-      </c>
-      <c r="D48">
-        <v>10660</v>
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E48">
+        <v>141667</v>
+      </c>
+      <c r="F48">
         <v>2350</v>
       </c>
-      <c r="F48">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G48">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2526</v>
       </c>
       <c r="B49" s="1">
         <v>45778</v>
       </c>
-      <c r="C49">
-        <v>127407</v>
-      </c>
-      <c r="D49">
-        <v>10951</v>
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E49">
+        <v>141667</v>
+      </c>
+      <c r="F49">
         <v>2350</v>
       </c>
-      <c r="F49">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G49">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2526</v>
       </c>
       <c r="B50" s="1">
         <v>45809</v>
       </c>
-      <c r="C50">
-        <v>127408</v>
-      </c>
-      <c r="D50">
-        <v>10659</v>
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E50">
+        <v>141667</v>
+      </c>
+      <c r="F50">
         <v>2350</v>
       </c>
-      <c r="F50">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G50">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2526</v>
       </c>
       <c r="B51" s="1">
         <v>45839</v>
       </c>
-      <c r="C51">
-        <v>127408</v>
-      </c>
-      <c r="D51">
-        <v>10659</v>
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E51">
+        <v>141667</v>
+      </c>
+      <c r="F51">
         <v>2350</v>
       </c>
-      <c r="F51">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G51">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2526</v>
       </c>
       <c r="B52" s="1">
         <v>45870</v>
       </c>
-      <c r="C52">
-        <v>127408</v>
-      </c>
-      <c r="D52">
-        <v>10659</v>
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E52">
+        <v>141667</v>
+      </c>
+      <c r="F52">
         <v>2350</v>
       </c>
-      <c r="F52">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G52">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2526</v>
       </c>
       <c r="B53" s="1">
         <v>45901</v>
       </c>
-      <c r="C53">
-        <v>149848</v>
-      </c>
-      <c r="D53">
-        <v>16552</v>
+      <c r="C53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E53">
+        <v>170000</v>
+      </c>
+      <c r="F53">
         <v>2350</v>
       </c>
-      <c r="F53">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G53">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2526</v>
       </c>
       <c r="B54" s="1">
         <v>45931</v>
       </c>
-      <c r="C54">
-        <v>149848</v>
-      </c>
-      <c r="D54">
-        <v>16552</v>
+      <c r="C54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E54">
+        <v>170000</v>
+      </c>
+      <c r="F54">
         <v>2350</v>
       </c>
-      <c r="F54">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G54">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2526</v>
       </c>
       <c r="B55" s="1">
         <v>45962</v>
       </c>
-      <c r="C55">
-        <v>149848</v>
-      </c>
-      <c r="D55">
-        <v>16552</v>
+      <c r="C55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E55">
+        <v>170000</v>
+      </c>
+      <c r="F55">
         <v>2350</v>
       </c>
-      <c r="F55">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G55">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2526</v>
       </c>
       <c r="B56" s="1">
         <v>45992</v>
       </c>
-      <c r="C56">
-        <v>149848</v>
-      </c>
-      <c r="D56">
-        <v>16552</v>
+      <c r="C56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E56">
+        <v>170000</v>
+      </c>
+      <c r="F56">
         <v>2350</v>
       </c>
-      <c r="F56">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G56">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2526</v>
       </c>
       <c r="B57" s="1">
         <v>46023</v>
       </c>
-      <c r="C57">
-        <v>146496</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
+      <c r="C57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E57">
+        <v>150096</v>
+      </c>
+      <c r="F57">
         <v>2350</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>1250</v>
       </c>
     </row>
@@ -1700,25 +1896,25 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1726,16 +1922,16 @@
         <v>44896</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1752,16 +1948,16 @@
         <v>44958</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1778,16 +1974,16 @@
         <v>45078</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1804,16 +2000,16 @@
         <v>45261</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1830,16 +2026,16 @@
         <v>45292</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1856,16 +2052,16 @@
         <v>45413</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1882,16 +2078,16 @@
         <v>45413</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1908,16 +2104,16 @@
         <v>45525</v>
       </c>
       <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1934,16 +2130,16 @@
         <v>45556</v>
       </c>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
         <v>27</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1960,16 +2156,16 @@
         <v>45586</v>
       </c>
       <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1986,16 +2182,16 @@
         <v>45617</v>
       </c>
       <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2012,16 +2208,16 @@
         <v>45647</v>
       </c>
       <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2038,16 +2234,16 @@
         <v>45678</v>
       </c>
       <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
         <v>27</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2064,16 +2260,16 @@
         <v>45709</v>
       </c>
       <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
         <v>27</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
-      </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2090,16 +2286,16 @@
         <v>45737</v>
       </c>
       <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
         <v>27</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2116,16 +2312,16 @@
         <v>45672</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2142,16 +2338,16 @@
         <v>45725</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2168,16 +2364,16 @@
         <v>45768</v>
       </c>
       <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
         <v>27</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2194,16 +2390,16 @@
         <v>45778</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2220,16 +2416,16 @@
         <v>45778</v>
       </c>
       <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
         <v>27</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21" t="s">
-        <v>28</v>
-      </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2246,16 +2442,16 @@
         <v>45809</v>
       </c>
       <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
         <v>27</v>
       </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22" t="s">
-        <v>28</v>
-      </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2272,16 +2468,16 @@
         <v>45839</v>
       </c>
       <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
         <v>27</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23" t="s">
-        <v>28</v>
-      </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2298,16 +2494,16 @@
         <v>45870</v>
       </c>
       <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
         <v>27</v>
       </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
-        <v>28</v>
-      </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2324,16 +2520,16 @@
         <v>45931</v>
       </c>
       <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
         <v>36</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" t="s">
-        <v>37</v>
-      </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2350,16 +2546,16 @@
         <v>45992</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2376,16 +2572,16 @@
         <v>45992</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2406,7 +2602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4760DB9E-5821-49E8-B842-9EABEB8E142E}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
@@ -2414,7 +2610,7 @@
     <col min="4" max="4" width="35.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2422,19 +2618,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
       <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2122</v>
       </c>
@@ -2442,10 +2641,10 @@
         <v>44377</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
       </c>
       <c r="E2">
         <v>32</v>
@@ -2453,8 +2652,11 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2122</v>
       </c>
@@ -2462,10 +2664,10 @@
         <v>44469</v>
       </c>
       <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
       </c>
       <c r="E3">
         <v>194</v>
@@ -2473,8 +2675,11 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2122</v>
       </c>
@@ -2482,10 +2687,10 @@
         <v>44561</v>
       </c>
       <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
       </c>
       <c r="E4">
         <v>194</v>
@@ -2493,8 +2698,11 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2122</v>
       </c>
@@ -2502,10 +2710,10 @@
         <v>44651</v>
       </c>
       <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
       </c>
       <c r="E5">
         <v>180</v>
@@ -2513,8 +2721,11 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2122</v>
       </c>
@@ -2522,10 +2733,10 @@
         <v>44651</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>587</v>
@@ -2533,8 +2744,11 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2223</v>
       </c>
@@ -2542,10 +2756,10 @@
         <v>44742</v>
       </c>
       <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
         <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
       </c>
       <c r="E7">
         <v>205</v>
@@ -2553,8 +2767,11 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2223</v>
       </c>
@@ -2562,10 +2779,10 @@
         <v>44834</v>
       </c>
       <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
         <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
       </c>
       <c r="E8">
         <v>605</v>
@@ -2573,8 +2790,11 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2223</v>
       </c>
@@ -2582,10 +2802,10 @@
         <v>44926</v>
       </c>
       <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
         <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
       </c>
       <c r="E9">
         <v>75</v>
@@ -2593,8 +2813,11 @@
       <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2223</v>
       </c>
@@ -2602,10 +2825,10 @@
         <v>44936</v>
       </c>
       <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
         <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
       </c>
       <c r="E10">
         <v>651.75</v>
@@ -2613,8 +2836,11 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2223</v>
       </c>
@@ -2622,10 +2848,10 @@
         <v>45016</v>
       </c>
       <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
         <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
       </c>
       <c r="E11">
         <v>89</v>
@@ -2633,8 +2859,11 @@
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2223</v>
       </c>
@@ -2642,10 +2871,10 @@
         <v>45016</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>4076</v>
@@ -2653,8 +2882,11 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2223</v>
       </c>
@@ -2662,10 +2894,10 @@
         <v>45016</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>118</v>
@@ -2673,8 +2905,11 @@
       <c r="F13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2324</v>
       </c>
@@ -2682,10 +2917,10 @@
         <v>45107</v>
       </c>
       <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
         <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
       </c>
       <c r="E14">
         <v>227</v>
@@ -2693,8 +2928,11 @@
       <c r="F14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2324</v>
       </c>
@@ -2702,10 +2940,10 @@
         <v>45199</v>
       </c>
       <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
         <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
       </c>
       <c r="E15">
         <v>151</v>
@@ -2713,8 +2951,11 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2324</v>
       </c>
@@ -2722,10 +2963,10 @@
         <v>45291</v>
       </c>
       <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
         <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
       </c>
       <c r="E16">
         <v>159</v>
@@ -2733,8 +2974,11 @@
       <c r="F16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2324</v>
       </c>
@@ -2742,10 +2986,10 @@
         <v>45382</v>
       </c>
       <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
         <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
       </c>
       <c r="E17">
         <v>63</v>
@@ -2753,8 +2997,11 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2324</v>
       </c>
@@ -2762,10 +3009,10 @@
         <v>45382</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18">
         <v>12707</v>
@@ -2773,8 +3020,11 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2324</v>
       </c>
@@ -2782,10 +3032,10 @@
         <v>45382</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>1488</v>
@@ -2793,8 +3043,11 @@
       <c r="F19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2324</v>
       </c>
@@ -2802,10 +3055,10 @@
         <v>45382</v>
       </c>
       <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
         <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
       </c>
       <c r="E20">
         <v>13485.92</v>
@@ -2813,8 +3066,11 @@
       <c r="F20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2324</v>
       </c>
@@ -2822,10 +3078,10 @@
         <v>45382</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E21">
         <v>9562.1200000000008</v>
@@ -2833,8 +3089,11 @@
       <c r="F21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2324</v>
       </c>
@@ -2842,10 +3101,10 @@
         <v>45382</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22">
         <v>3231.38</v>
@@ -2853,8 +3112,11 @@
       <c r="F22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2425</v>
       </c>
@@ -2862,10 +3124,10 @@
         <v>45473</v>
       </c>
       <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
         <v>11</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
       </c>
       <c r="E23">
         <v>101</v>
@@ -2873,8 +3135,11 @@
       <c r="F23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2425</v>
       </c>
@@ -2882,10 +3147,10 @@
         <v>45475</v>
       </c>
       <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
         <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
       </c>
       <c r="E24">
         <v>2732</v>
@@ -2893,8 +3158,11 @@
       <c r="F24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2425</v>
       </c>
@@ -2902,10 +3170,10 @@
         <v>45475</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <v>3608</v>
@@ -2913,8 +3181,11 @@
       <c r="F25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2425</v>
       </c>
@@ -2922,10 +3193,10 @@
         <v>45402</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26">
         <v>1275</v>
@@ -2933,8 +3204,11 @@
       <c r="F26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2425</v>
       </c>
@@ -2942,10 +3216,10 @@
         <v>45565</v>
       </c>
       <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
         <v>11</v>
-      </c>
-      <c r="D27" t="s">
-        <v>12</v>
       </c>
       <c r="E27">
         <v>101</v>
@@ -2953,8 +3227,11 @@
       <c r="F27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2425</v>
       </c>
@@ -2962,10 +3239,10 @@
         <v>45657</v>
       </c>
       <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
         <v>11</v>
-      </c>
-      <c r="D28" t="s">
-        <v>12</v>
       </c>
       <c r="E28">
         <v>312</v>
@@ -2973,8 +3250,11 @@
       <c r="F28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2425</v>
       </c>
@@ -2982,10 +3262,10 @@
         <v>45382</v>
       </c>
       <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
         <v>11</v>
-      </c>
-      <c r="D29" t="s">
-        <v>12</v>
       </c>
       <c r="E29">
         <v>289</v>
@@ -2993,8 +3273,11 @@
       <c r="F29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2425</v>
       </c>
@@ -3002,10 +3285,10 @@
         <v>45747</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>1889</v>
@@ -3013,8 +3296,11 @@
       <c r="F30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2425</v>
       </c>
@@ -3022,10 +3308,10 @@
         <v>45747</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31">
         <v>15821</v>
@@ -3033,8 +3319,11 @@
       <c r="F31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2425</v>
       </c>
@@ -3042,10 +3331,10 @@
         <v>45747</v>
       </c>
       <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" t="s">
         <v>27</v>
-      </c>
-      <c r="D32" t="s">
-        <v>28</v>
       </c>
       <c r="E32">
         <v>4659</v>
@@ -3053,8 +3342,11 @@
       <c r="F32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2526</v>
       </c>
@@ -3062,10 +3354,10 @@
         <v>45786</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E33">
         <v>2619</v>
@@ -3073,8 +3365,11 @@
       <c r="F33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2526</v>
       </c>
@@ -3082,10 +3377,10 @@
         <v>45838</v>
       </c>
       <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
         <v>11</v>
-      </c>
-      <c r="D34" t="s">
-        <v>12</v>
       </c>
       <c r="E34">
         <v>238</v>
@@ -3093,8 +3388,11 @@
       <c r="F34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2526</v>
       </c>
@@ -3102,10 +3400,10 @@
         <v>45930</v>
       </c>
       <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="s">
         <v>11</v>
-      </c>
-      <c r="D35" t="s">
-        <v>12</v>
       </c>
       <c r="E35">
         <v>126</v>
@@ -3113,8 +3411,11 @@
       <c r="F35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2526</v>
       </c>
@@ -3122,10 +3423,10 @@
         <v>45900</v>
       </c>
       <c r="C36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" t="s">
         <v>27</v>
-      </c>
-      <c r="D36" t="s">
-        <v>28</v>
       </c>
       <c r="E36">
         <v>7497</v>
@@ -3133,8 +3434,11 @@
       <c r="F36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2526</v>
       </c>
@@ -3142,16 +3446,24 @@
         <v>46022</v>
       </c>
       <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s">
         <v>11</v>
-      </c>
-      <c r="D37" t="s">
-        <v>12</v>
       </c>
       <c r="E37">
         <v>222</v>
       </c>
       <c r="F37">
         <v>0</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D40" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3160,6 +3472,906 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829B0B7C-2A1B-4BB4-A016-16389A03F40E}">
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2223</v>
+      </c>
+      <c r="B2" s="1">
+        <v>44713</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2223</v>
+      </c>
+      <c r="B3" s="1">
+        <v>44743</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2223</v>
+      </c>
+      <c r="B4" s="1">
+        <v>44774</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2223</v>
+      </c>
+      <c r="B5" s="1">
+        <v>44805</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2223</v>
+      </c>
+      <c r="B6" s="1">
+        <v>44835</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2223</v>
+      </c>
+      <c r="B7" s="1">
+        <v>44866</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2223</v>
+      </c>
+      <c r="B8" s="1">
+        <v>44896</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2223</v>
+      </c>
+      <c r="B9" s="1">
+        <v>44927</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2223</v>
+      </c>
+      <c r="B10" s="1">
+        <v>44958</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2223</v>
+      </c>
+      <c r="B11" s="1">
+        <v>44986</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>200</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2324</v>
+      </c>
+      <c r="B12" s="1">
+        <v>45017</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>2975</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2324</v>
+      </c>
+      <c r="B13" s="1">
+        <v>45047</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13">
+        <v>2853</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2324</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45078</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14">
+        <v>2720</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2324</v>
+      </c>
+      <c r="B15" s="1">
+        <v>45108</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15">
+        <v>2572</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2324</v>
+      </c>
+      <c r="B16" s="1">
+        <v>45139</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16">
+        <v>2406</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2324</v>
+      </c>
+      <c r="B17" s="1">
+        <v>45170</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17">
+        <v>2215</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2324</v>
+      </c>
+      <c r="B18" s="1">
+        <v>45200</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18">
+        <v>4957</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2324</v>
+      </c>
+      <c r="B19" s="1">
+        <v>45231</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19">
+        <v>4691</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2324</v>
+      </c>
+      <c r="B20" s="1">
+        <v>45261</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20">
+        <v>4358</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2324</v>
+      </c>
+      <c r="B21" s="1">
+        <v>45292</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21">
+        <v>3914</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2324</v>
+      </c>
+      <c r="B22" s="1">
+        <v>45323</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22">
+        <v>4762</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2324</v>
+      </c>
+      <c r="B23" s="1">
+        <v>45352</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23">
+        <v>3605</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2425</v>
+      </c>
+      <c r="B24" s="1">
+        <v>45383</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24">
+        <v>7056</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2425</v>
+      </c>
+      <c r="B25" s="1">
+        <v>45413</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25">
+        <v>6935</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>2425</v>
+      </c>
+      <c r="B26" s="1">
+        <v>45444</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26">
+        <v>6801</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>2425</v>
+      </c>
+      <c r="B27" s="1">
+        <v>45474</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27">
+        <v>6654</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>2425</v>
+      </c>
+      <c r="B28" s="1">
+        <v>45536</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28">
+        <v>6320</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2425</v>
+      </c>
+      <c r="B29" s="1">
+        <v>45566</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29">
+        <v>6321</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>2425</v>
+      </c>
+      <c r="B30" s="1">
+        <v>45597</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30">
+        <v>6321</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>2425</v>
+      </c>
+      <c r="B31" s="1">
+        <v>45627</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31">
+        <v>6321</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2425</v>
+      </c>
+      <c r="B32" s="1">
+        <v>45658</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32">
+        <v>19992</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>2425</v>
+      </c>
+      <c r="B33" s="1">
+        <v>45689</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33">
+        <v>19992</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>2425</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45717</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34">
+        <v>19991</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>2526</v>
+      </c>
+      <c r="B35" s="1">
+        <v>45748</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35">
+        <v>10660</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>2526</v>
+      </c>
+      <c r="B36" s="1">
+        <v>45778</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36">
+        <v>291</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>2526</v>
+      </c>
+      <c r="B37" s="1">
+        <v>45778</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37">
+        <v>10660</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>2526</v>
+      </c>
+      <c r="B38" s="1">
+        <v>45809</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38">
+        <v>10659</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>2526</v>
+      </c>
+      <c r="B39" s="1">
+        <v>45839</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39">
+        <v>10659</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>2526</v>
+      </c>
+      <c r="B40" s="1">
+        <v>45870</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40">
+        <v>10659</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>2526</v>
+      </c>
+      <c r="B41" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E41">
+        <v>16552</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>2526</v>
+      </c>
+      <c r="B42" s="1">
+        <v>45931</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42">
+        <v>16552</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>2526</v>
+      </c>
+      <c r="B43" s="1">
+        <v>45962</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43">
+        <v>16552</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2526</v>
+      </c>
+      <c r="B44" s="1">
+        <v>45992</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44">
+        <v>16552</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0E7D11-5DD3-425F-AF3D-D34510F17951}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3179,19 +4391,19 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
         <v>33</v>
-      </c>
-      <c r="G1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -3202,10 +4414,10 @@
         <v>45321</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3225,10 +4437,10 @@
         <v>45746</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3248,10 +4460,10 @@
         <v>45757</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3271,10 +4483,10 @@
         <v>46001</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>0</v>
